--- a/docs/hub/estate/Planning and Insight/Reports/1052-53/1052-12-01_Student-Numbers-Return-1052-53_v01.xlsx
+++ b/docs/hub/estate/Planning and Insight/Reports/1052-53/1052-12-01_Student-Numbers-Return-1052-53_v01.xlsx
@@ -428,7 +428,7 @@
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2729</v>
+        <v>3366</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2107</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>622</v>
+        <v>900</v>
       </c>
     </row>
     <row r="5">
@@ -490,11 +490,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>197</v>
+        <v>288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Year 1 121 and Year 2 76</t>
+          <t>Year 1 108; Year 2 89; Year 3 91</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7">
@@ -515,11 +515,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>923</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Three-year programmes only</t>
+          <t>All twelve programmes</t>
         </is>
       </c>
     </row>
@@ -530,11 +530,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>815</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Finalists on three-year programmes</t>
+          <t>Finalists</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Two-year programmes (Nursing and Care Midwifery Herbal Practice Integrated Mind-Body and all Education programmes) do not produce honours graduates or NSS finalists.</t>
+          <t>All Faculty programmes are three-year honours programmes. The Diploma of Higher Education is an exit award only.</t>
         </is>
       </c>
     </row>
